--- a/docs/Test_Report/TestPlanExecutionReport.xlsx
+++ b/docs/Test_Report/TestPlanExecutionReport.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2025-11-19 05:58:54.356285-06:00 CDT</t>
+          <t>2025-11-20 04:14:42.908612-06:00 CDT</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28162,MCAL-28163,MCAL-25808,MCAL-25806,MCAL-25807,MCAL-25801,MCAL-25799,MCAL-25797,MCAL-25811,MCAL-25810,MCAL-25809,MCAL-25804,MCAL-25803,MCAL-25802,MCAL-25798,MCAL-25796,MCAL-25805,MCAL-25800,MCAL-28161,MCAL-25820,MCAL-28165,MCAL-28164,MCAL-25812</t>
+          <t>MCAL-28162,MCAL-28163,MCAL-25808,MCAL-25806,MCAL-25807,MCAL-25801,MCAL-25799,MCAL-25800,MCAL-25820,MCAL-28165,MCAL-28164,MCAL-25797,MCAL-25812,MCAL-25811,MCAL-25810,MCAL-28161,MCAL-25809,MCAL-25804,MCAL-25803,MCAL-25802,MCAL-25798,MCAL-25796,MCAL-25805</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25814,MCAL-25721,MCAL-25720,MCAL-25717,MCAL-25712,MCAL-25711,MCAL-25701,MCAL-25715,MCAL-25704,MCAL-25702,MCAL-25716,MCAL-25718,MCAL-25706,MCAL-25709,MCAL-25708,MCAL-25707,MCAL-25813,MCAL-25710,MCAL-25705,MCAL-25714,MCAL-25713,MCAL-25723,MCAL-25731,MCAL-25727,MCAL-25726,MCAL-25724,MCAL-25725,MCAL-28133,MCAL-25703,MCAL-25824,MCAL-25823,MCAL-25732,MCAL-25722,MCAL-25719,MCAL-28135,MCAL-25825,MCAL-28134,MCAL-25822,MCAL-25730,MCAL-25729,MCAL-25728</t>
+          <t>MCAL-25814,MCAL-25721,MCAL-25720,MCAL-25717,MCAL-25712,MCAL-25711,MCAL-25701,MCAL-25715,MCAL-25704,MCAL-25702,MCAL-25716,MCAL-25718,MCAL-25706,MCAL-25709,MCAL-25708,MCAL-25707,MCAL-25813,MCAL-25723,MCAL-25731,MCAL-25727,MCAL-25726,MCAL-25724,MCAL-25725,MCAL-28133,MCAL-25703,MCAL-25824,MCAL-25823,MCAL-25732,MCAL-25722,MCAL-25719,MCAL-28135,MCAL-25825,MCAL-25710,MCAL-25705,MCAL-25714,MCAL-25713,MCAL-28134,MCAL-25822,MCAL-25730,MCAL-25729,MCAL-25728</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Architecture,Design,Design,Design,Design,Design,Design,Architecture,Design,Design,Design,Design,Architecture,Architecture,Architecture,Architecture,Architecture,Design,Architecture</t>
+          <t>Architecture,Design,Design,Design,Design,Design,Design,Architecture,Design,Design,Design,Design,Architecture,Architecture,Architecture,Design,Architecture,Architecture,Architecture</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25189,MCAL-25530,MCAL-25533,MCAL-25534,MCAL-25535,MCAL-25538,MCAL-25540,MCAL-25190,MCAL-25531,MCAL-25532,MCAL-25537,MCAL-25539,MCAL-28233,MCAL-25192,MCAL-25194,MCAL-25195,MCAL-25191,MCAL-25536,MCAL-25193</t>
+          <t>MCAL-25189,MCAL-25530,MCAL-25533,MCAL-25534,MCAL-25535,MCAL-25538,MCAL-25540,MCAL-25190,MCAL-25531,MCAL-25532,MCAL-25537,MCAL-25539,MCAL-28233,MCAL-25192,MCAL-25194,MCAL-25536,MCAL-25195,MCAL-25191,MCAL-25193</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Architecture,Design,Architecture,Design,Architecture,Architecture,Architecture,Design,Design,Architecture,Architecture,Design,Design,Design</t>
+          <t>Architecture,Design,Architecture,Design,Architecture,Design,Design,Architecture,Architecture,Design,Architecture,Architecture,Design,Design</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25190,MCAL-25592,MCAL-25191,MCAL-25590,MCAL-25192,MCAL-25194,MCAL-25195,MCAL-25591,MCAL-25688,MCAL-25193,MCAL-25189,MCAL-25690,MCAL-25691,MCAL-25689</t>
+          <t>MCAL-25190,MCAL-25592,MCAL-25191,MCAL-25590,MCAL-25195,MCAL-25591,MCAL-25688,MCAL-25193,MCAL-25189,MCAL-25690,MCAL-25192,MCAL-25194,MCAL-25691,MCAL-25689</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-24888,MCAL-25066,MCAL-25068,MCAL-25060,MCAL-25061,MCAL-25051,MCAL-25111,MCAL-28292,MCAL-24983,MCAL-24951,MCAL-25059,MCAL-25065,MCAL-24956</t>
+          <t>MCAL-24888,MCAL-25066,MCAL-25068,MCAL-25060,MCAL-25061,MCAL-25051,MCAL-25111,MCAL-28292,MCAL-24983,MCAL-24951,MCAL-24956,MCAL-25065,MCAL-25059</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">

--- a/docs/Test_Report/TestPlanExecutionReport.xlsx
+++ b/docs/Test_Report/TestPlanExecutionReport.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20 04:14:42.908612-06:00 CDT</t>
+          <t>2025-11-20 07:48:52.067655-06:00 CDT</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28162,MCAL-28163,MCAL-25808,MCAL-25806,MCAL-25807,MCAL-25801,MCAL-25799,MCAL-25800,MCAL-25820,MCAL-28165,MCAL-28164,MCAL-25797,MCAL-25812,MCAL-25811,MCAL-25810,MCAL-28161,MCAL-25809,MCAL-25804,MCAL-25803,MCAL-25802,MCAL-25798,MCAL-25796,MCAL-25805</t>
+          <t>MCAL-28162,MCAL-28163,MCAL-25808,MCAL-25806,MCAL-25807,MCAL-25801,MCAL-25799,MCAL-25820,MCAL-28165,MCAL-28164,MCAL-25797,MCAL-25812,MCAL-25811,MCAL-25810,MCAL-28161,MCAL-25809,MCAL-25804,MCAL-25803,MCAL-25802,MCAL-25798,MCAL-25796,MCAL-25805,MCAL-25800</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25814,MCAL-25721,MCAL-25720,MCAL-25717,MCAL-25712,MCAL-25711,MCAL-25701,MCAL-25715,MCAL-25704,MCAL-25702,MCAL-25716,MCAL-25718,MCAL-25706,MCAL-25709,MCAL-25708,MCAL-25707,MCAL-25813,MCAL-25723,MCAL-25731,MCAL-25727,MCAL-25726,MCAL-25724,MCAL-25725,MCAL-28133,MCAL-25703,MCAL-25824,MCAL-25823,MCAL-25732,MCAL-25722,MCAL-25719,MCAL-28135,MCAL-25825,MCAL-25710,MCAL-25705,MCAL-25714,MCAL-25713,MCAL-28134,MCAL-25822,MCAL-25730,MCAL-25729,MCAL-25728</t>
+          <t>MCAL-25814,MCAL-25721,MCAL-25720,MCAL-25717,MCAL-25712,MCAL-25711,MCAL-25701,MCAL-25715,MCAL-25704,MCAL-25702,MCAL-25716,MCAL-25718,MCAL-25709,MCAL-25708,MCAL-25707,MCAL-25706,MCAL-25731,MCAL-25727,MCAL-25726,MCAL-25724,MCAL-25725,MCAL-28133,MCAL-25703,MCAL-25824,MCAL-25823,MCAL-25813,MCAL-25732,MCAL-25722,MCAL-25719,MCAL-28135,MCAL-25825,MCAL-25710,MCAL-25705,MCAL-25714,MCAL-25713,MCAL-28134,MCAL-25822,MCAL-25730,MCAL-25729,MCAL-25728,MCAL-25723</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Architecture,Design,Design,Design,Design,Design,Design,Architecture,Design,Design,Design,Design,Architecture,Architecture,Architecture,Design,Architecture,Architecture,Architecture</t>
+          <t>Architecture,Design,Design,Design,Design,Design,Design,Architecture,Design,Design,Design,Design,Architecture,Architecture,Architecture,Architecture,Design,Architecture,Architecture</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25189,MCAL-25530,MCAL-25533,MCAL-25534,MCAL-25535,MCAL-25538,MCAL-25540,MCAL-25190,MCAL-25531,MCAL-25532,MCAL-25537,MCAL-25539,MCAL-28233,MCAL-25192,MCAL-25194,MCAL-25536,MCAL-25195,MCAL-25191,MCAL-25193</t>
+          <t>MCAL-25189,MCAL-25530,MCAL-25533,MCAL-25534,MCAL-25535,MCAL-25538,MCAL-25540,MCAL-25190,MCAL-25531,MCAL-25532,MCAL-25537,MCAL-25539,MCAL-28233,MCAL-25191,MCAL-25192,MCAL-25194,MCAL-25536,MCAL-25193,MCAL-25195</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Architecture,Design,Architecture,Design,Architecture,Design,Design,Architecture,Architecture,Design,Architecture,Architecture,Design,Design</t>
+          <t>Architecture,Design,Architecture,Design,Design,Architecture,Architecture,Architecture,Design,Design,Design,Design,Architecture,Architecture</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25190,MCAL-25592,MCAL-25191,MCAL-25590,MCAL-25195,MCAL-25591,MCAL-25688,MCAL-25193,MCAL-25189,MCAL-25690,MCAL-25192,MCAL-25194,MCAL-25691,MCAL-25689</t>
+          <t>MCAL-25190,MCAL-25592,MCAL-25191,MCAL-25590,MCAL-25690,MCAL-25192,MCAL-25194,MCAL-25195,MCAL-25691,MCAL-25591,MCAL-25689,MCAL-25688,MCAL-25189,MCAL-25193</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25577,MCAL-25682,MCAL-25685,MCAL-25542,MCAL-25543,MCAL-25670,MCAL-25642,MCAL-25643,MCAL-25644,MCAL-25541,MCAL-25601,MCAL-25696,MCAL-25698,MCAL-25691</t>
+          <t>MCAL-25577,MCAL-25682,MCAL-25685,MCAL-25542,MCAL-25543,MCAL-25670,MCAL-25642,MCAL-25643,MCAL-25644,MCAL-25601,MCAL-25696,MCAL-25698,MCAL-25691,MCAL-25541</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25615,MCAL-25617,MCAL-25619,MCAL-25642,MCAL-25662,MCAL-25699,MCAL-25553,MCAL-25558,MCAL-25552,MCAL-25575,MCAL-25576,MCAL-25616,MCAL-25680,MCAL-25618,MCAL-25681,MCAL-25673,MCAL-25696,MCAL-25698,MCAL-25689,MCAL-25690,MCAL-25620</t>
+          <t>MCAL-25615,MCAL-25617,MCAL-25619,MCAL-25642,MCAL-25662,MCAL-25699,MCAL-25553,MCAL-25558,MCAL-25552,MCAL-25575,MCAL-25576,MCAL-25616,MCAL-25680,MCAL-25620,MCAL-25618,MCAL-25681,MCAL-25673,MCAL-25696,MCAL-25698,MCAL-25689,MCAL-25690</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25560,MCAL-25565,MCAL-25569,MCAL-25572,MCAL-25607,MCAL-25609,MCAL-25675,MCAL-25636,MCAL-25567,MCAL-25568,MCAL-25574,MCAL-25606,MCAL-25683,MCAL-25635,MCAL-25610,MCAL-25638,MCAL-25562,MCAL-25559,MCAL-25563,MCAL-25608,MCAL-25698,MCAL-25673,MCAL-25688,MCAL-25696,MCAL-25637,MCAL-25678,MCAL-25573</t>
+          <t>MCAL-25560,MCAL-25565,MCAL-25569,MCAL-25572,MCAL-25607,MCAL-25609,MCAL-25675,MCAL-25636,MCAL-25567,MCAL-25568,MCAL-25574,MCAL-25606,MCAL-25683,MCAL-25635,MCAL-25610,MCAL-25638,MCAL-25562,MCAL-25559,MCAL-25678,MCAL-25573,MCAL-25637,MCAL-25563,MCAL-25608,MCAL-25698,MCAL-25673,MCAL-25688,MCAL-25696</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25610,MCAL-25566,MCAL-25570,MCAL-25571,MCAL-25572,MCAL-25609,MCAL-25613,MCAL-25614,MCAL-25560,MCAL-25561,MCAL-25569,MCAL-25564,MCAL-25574,MCAL-25567,MCAL-25562,MCAL-25607,MCAL-25608,MCAL-25611,MCAL-25612,MCAL-25606,MCAL-25568,MCAL-25559,MCAL-25573,MCAL-25563,MCAL-25565</t>
+          <t>MCAL-25610,MCAL-25566,MCAL-25570,MCAL-25571,MCAL-25572,MCAL-25609,MCAL-25613,MCAL-25614,MCAL-25560,MCAL-25561,MCAL-25569,MCAL-25559,MCAL-25573,MCAL-25564,MCAL-25574,MCAL-25563,MCAL-25565,MCAL-25568,MCAL-25567,MCAL-25562,MCAL-25607,MCAL-25608,MCAL-25611,MCAL-25612,MCAL-25606</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-12327,MCAL-12315,MCAL-12340,MCAL-12359,MCAL-12421,MCAL-12427,MCAL-12341,MCAL-12307,MCAL-12345,MCAL-12391,MCAL-12326,MCAL-12338,MCAL-12414,MCAL-12438,MCAL-12393,MCAL-12362,MCAL-12394,MCAL-12372,MCAL-12376,MCAL-12343,MCAL-12378,MCAL-12342,MCAL-12426,MCAL-12412,MCAL-12329,MCAL-12373,MCAL-12344,MCAL-12308,MCAL-12388,MCAL-12411,MCAL-12346,MCAL-12385,MCAL-12387,MCAL-12353,MCAL-12375,MCAL-12435,MCAL-12354,MCAL-12434,MCAL-12424,MCAL-12347,MCAL-12323,MCAL-12416,MCAL-12306,MCAL-12356,MCAL-12358,MCAL-12374,MCAL-12339,MCAL-12415,MCAL-12304,MCAL-12377</t>
+          <t>MCAL-12327,MCAL-12315,MCAL-12340,MCAL-12359,MCAL-12421,MCAL-12427,MCAL-12341,MCAL-12307,MCAL-12345,MCAL-12391,MCAL-12326,MCAL-12338,MCAL-12414,MCAL-12438,MCAL-12393,MCAL-12362,MCAL-12394,MCAL-12372,MCAL-12376,MCAL-12343,MCAL-12378,MCAL-12342,MCAL-12426,MCAL-12412,MCAL-12329,MCAL-12373,MCAL-12344,MCAL-12308,MCAL-12388,MCAL-12411,MCAL-12346,MCAL-12385,MCAL-12387,MCAL-12353,MCAL-12375,MCAL-12435,MCAL-12354,MCAL-12434,MCAL-12424,MCAL-12347,MCAL-12323,MCAL-12416,MCAL-12306,MCAL-12356,MCAL-12358,MCAL-12374,MCAL-12415,MCAL-12304,MCAL-12377,MCAL-12339</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-24888,MCAL-25066,MCAL-25068,MCAL-25060,MCAL-25061,MCAL-25051,MCAL-25111,MCAL-28292,MCAL-24983,MCAL-24951,MCAL-24956,MCAL-25065,MCAL-25059</t>
+          <t>MCAL-24888,MCAL-25066,MCAL-25068,MCAL-25060,MCAL-25061,MCAL-25051,MCAL-25111,MCAL-28292,MCAL-24983,MCAL-24951,MCAL-25059,MCAL-25065,MCAL-24956</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25158,MCAL-25145,MCAL-25142,MCAL-25171,MCAL-25138,MCAL-25139,MCAL-25140,MCAL-25143,MCAL-25144,MCAL-25146,MCAL-25157,MCAL-25147,MCAL-25141,MCAL-28104</t>
+          <t>MCAL-25158,MCAL-25145,MCAL-25142,MCAL-25171,MCAL-25138,MCAL-25139,MCAL-25140,MCAL-25143,MCAL-25144,MCAL-25146,MCAL-25157,MCAL-25147,MCAL-28104,MCAL-25141</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25107,MCAL-25113,MCAL-24861,MCAL-25108,MCAL-25115,MCAL-25114,MCAL-25105,MCAL-25106,MCAL-25110,MCAL-25111,MCAL-25112,MCAL-25109</t>
+          <t>MCAL-25107,MCAL-25113,MCAL-24861,MCAL-25108,MCAL-25115,MCAL-25114,MCAL-25105,MCAL-25109,MCAL-25106,MCAL-25110,MCAL-25111,MCAL-25112</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>MCAL-24881,MCAL-24878,MCAL-24852,MCAL-24850,MCAL-24890,MCAL-25030,MCAL-25089,MCAL-24877,MCAL-24857,MCAL-24851,MCAL-24856</t>
+          <t>MCAL-24881,MCAL-24878,MCAL-24852,MCAL-24850,MCAL-24890,MCAL-25030,MCAL-25089,MCAL-24877,MCAL-24857,MCAL-24856,MCAL-24851</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30520,MCAL-30527,MCAL-30529,MCAL-30518,MCAL-30531,MCAL-30525,MCAL-30530,MCAL-30532,MCAL-30519,MCAL-30528,MCAL-30526,MCAL-30521,MCAL-30524,MCAL-30522,MCAL-30523</t>
+          <t>MCAL-30520,MCAL-30527,MCAL-30529,MCAL-30518,MCAL-30531,MCAL-30525,MCAL-30530,MCAL-30532,MCAL-30519,MCAL-30528,MCAL-30521,MCAL-30524,MCAL-30522,MCAL-30523,MCAL-30526</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
@@ -15602,7 +15602,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30551,MCAL-30552,MCAL-30554,MCAL-30557,MCAL-30558,MCAL-30569,MCAL-30570,MCAL-30572,MCAL-30575,MCAL-30576,MCAL-30559,MCAL-30563,MCAL-30566,MCAL-30556,MCAL-30553,MCAL-30555,MCAL-30561,MCAL-30573,MCAL-30550,MCAL-30562,MCAL-30564,MCAL-30565,MCAL-30567,MCAL-30568,MCAL-30574,MCAL-30571,MCAL-30560</t>
+          <t>MCAL-30551,MCAL-30552,MCAL-30554,MCAL-30557,MCAL-30558,MCAL-30569,MCAL-30570,MCAL-30572,MCAL-30575,MCAL-30576,MCAL-30559,MCAL-30563,MCAL-30566,MCAL-30556,MCAL-30553,MCAL-30555,MCAL-30561,MCAL-30573,MCAL-30550,MCAL-30562,MCAL-30564,MCAL-30565,MCAL-30567,MCAL-30568,MCAL-30574,MCAL-30560,MCAL-30571</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">

--- a/docs/Test_Report/TestPlanExecutionReport.xlsx
+++ b/docs/Test_Report/TestPlanExecutionReport.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20 07:48:52.067655-06:00 CDT</t>
+          <t>2025-11-20 11:43:19.837024-06:00 CDT</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28162,MCAL-28163,MCAL-25808,MCAL-25806,MCAL-25807,MCAL-25801,MCAL-25799,MCAL-25820,MCAL-28165,MCAL-28164,MCAL-25797,MCAL-25812,MCAL-25811,MCAL-25810,MCAL-28161,MCAL-25809,MCAL-25804,MCAL-25803,MCAL-25802,MCAL-25798,MCAL-25796,MCAL-25805,MCAL-25800</t>
+          <t>MCAL-28162,MCAL-28163,MCAL-25808,MCAL-25806,MCAL-25807,MCAL-25801,MCAL-25799,MCAL-25800,MCAL-25820,MCAL-28165,MCAL-28164,MCAL-25797,MCAL-25812,MCAL-25811,MCAL-25810,MCAL-28161,MCAL-25809,MCAL-25804,MCAL-25803,MCAL-25802,MCAL-25798,MCAL-25796,MCAL-25805</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25814,MCAL-25721,MCAL-25720,MCAL-25717,MCAL-25712,MCAL-25711,MCAL-25701,MCAL-25715,MCAL-25704,MCAL-25702,MCAL-25716,MCAL-25718,MCAL-25709,MCAL-25708,MCAL-25707,MCAL-25706,MCAL-25731,MCAL-25727,MCAL-25726,MCAL-25724,MCAL-25725,MCAL-28133,MCAL-25703,MCAL-25824,MCAL-25823,MCAL-25813,MCAL-25732,MCAL-25722,MCAL-25719,MCAL-28135,MCAL-25825,MCAL-25710,MCAL-25705,MCAL-25714,MCAL-25713,MCAL-28134,MCAL-25822,MCAL-25730,MCAL-25729,MCAL-25728,MCAL-25723</t>
+          <t>MCAL-25814,MCAL-25721,MCAL-25720,MCAL-25717,MCAL-25712,MCAL-25711,MCAL-25701,MCAL-25715,MCAL-25704,MCAL-25702,MCAL-25716,MCAL-25718,MCAL-25706,MCAL-25709,MCAL-25708,MCAL-25707,MCAL-25813,MCAL-25723,MCAL-25731,MCAL-25727,MCAL-25726,MCAL-25724,MCAL-25725,MCAL-28133,MCAL-25703,MCAL-25824,MCAL-25823,MCAL-25732,MCAL-25722,MCAL-25719,MCAL-28135,MCAL-25825,MCAL-25710,MCAL-25705,MCAL-25714,MCAL-25713,MCAL-28134,MCAL-25822,MCAL-25730,MCAL-25729,MCAL-25728</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Architecture,Design,Design,Design,Design,Design,Design,Architecture,Design,Design,Design,Design,Architecture,Architecture,Architecture,Architecture,Design,Architecture,Architecture</t>
+          <t>Architecture,Design,Design,Design,Design,Design,Design,Architecture,Design,Design,Design,Design,Architecture,Architecture,Architecture,Architecture,Architecture,Design,Architecture</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25189,MCAL-25530,MCAL-25533,MCAL-25534,MCAL-25535,MCAL-25538,MCAL-25540,MCAL-25190,MCAL-25531,MCAL-25532,MCAL-25537,MCAL-25539,MCAL-28233,MCAL-25191,MCAL-25192,MCAL-25194,MCAL-25536,MCAL-25193,MCAL-25195</t>
+          <t>MCAL-25189,MCAL-25530,MCAL-25533,MCAL-25534,MCAL-25535,MCAL-25538,MCAL-25540,MCAL-25190,MCAL-25531,MCAL-25532,MCAL-25537,MCAL-25539,MCAL-28233,MCAL-25192,MCAL-25194,MCAL-25195,MCAL-25191,MCAL-25536,MCAL-25193</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Architecture,Design,Architecture,Design,Design,Architecture,Architecture,Architecture,Design,Design,Design,Design,Architecture,Architecture</t>
+          <t>Architecture,Design,Architecture,Design,Architecture,Design,Design,Architecture,Architecture,Design,Architecture,Architecture,Design,Design</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25190,MCAL-25592,MCAL-25191,MCAL-25590,MCAL-25690,MCAL-25192,MCAL-25194,MCAL-25195,MCAL-25691,MCAL-25591,MCAL-25689,MCAL-25688,MCAL-25189,MCAL-25193</t>
+          <t>MCAL-25190,MCAL-25592,MCAL-25191,MCAL-25590,MCAL-25195,MCAL-25591,MCAL-25688,MCAL-25193,MCAL-25189,MCAL-25690,MCAL-25192,MCAL-25194,MCAL-25691,MCAL-25689</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25577,MCAL-25682,MCAL-25685,MCAL-25542,MCAL-25543,MCAL-25670,MCAL-25642,MCAL-25643,MCAL-25644,MCAL-25601,MCAL-25696,MCAL-25698,MCAL-25691,MCAL-25541</t>
+          <t>MCAL-25577,MCAL-25682,MCAL-25685,MCAL-25542,MCAL-25543,MCAL-25670,MCAL-25642,MCAL-25643,MCAL-25644,MCAL-25541,MCAL-25601,MCAL-25696,MCAL-25698,MCAL-25691</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25615,MCAL-25617,MCAL-25619,MCAL-25642,MCAL-25662,MCAL-25699,MCAL-25553,MCAL-25558,MCAL-25552,MCAL-25575,MCAL-25576,MCAL-25616,MCAL-25680,MCAL-25620,MCAL-25618,MCAL-25681,MCAL-25673,MCAL-25696,MCAL-25698,MCAL-25689,MCAL-25690</t>
+          <t>MCAL-25615,MCAL-25617,MCAL-25619,MCAL-25642,MCAL-25662,MCAL-25699,MCAL-25553,MCAL-25558,MCAL-25552,MCAL-25575,MCAL-25576,MCAL-25616,MCAL-25680,MCAL-25618,MCAL-25681,MCAL-25673,MCAL-25696,MCAL-25698,MCAL-25689,MCAL-25690,MCAL-25620</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25560,MCAL-25565,MCAL-25569,MCAL-25572,MCAL-25607,MCAL-25609,MCAL-25675,MCAL-25636,MCAL-25567,MCAL-25568,MCAL-25574,MCAL-25606,MCAL-25683,MCAL-25635,MCAL-25610,MCAL-25638,MCAL-25562,MCAL-25559,MCAL-25678,MCAL-25573,MCAL-25637,MCAL-25563,MCAL-25608,MCAL-25698,MCAL-25673,MCAL-25688,MCAL-25696</t>
+          <t>MCAL-25560,MCAL-25565,MCAL-25569,MCAL-25572,MCAL-25607,MCAL-25609,MCAL-25675,MCAL-25636,MCAL-25567,MCAL-25568,MCAL-25574,MCAL-25606,MCAL-25683,MCAL-25635,MCAL-25610,MCAL-25638,MCAL-25562,MCAL-25559,MCAL-25563,MCAL-25608,MCAL-25698,MCAL-25673,MCAL-25688,MCAL-25696,MCAL-25637,MCAL-25678,MCAL-25573</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25610,MCAL-25566,MCAL-25570,MCAL-25571,MCAL-25572,MCAL-25609,MCAL-25613,MCAL-25614,MCAL-25560,MCAL-25561,MCAL-25569,MCAL-25559,MCAL-25573,MCAL-25564,MCAL-25574,MCAL-25563,MCAL-25565,MCAL-25568,MCAL-25567,MCAL-25562,MCAL-25607,MCAL-25608,MCAL-25611,MCAL-25612,MCAL-25606</t>
+          <t>MCAL-25610,MCAL-25566,MCAL-25570,MCAL-25571,MCAL-25572,MCAL-25609,MCAL-25613,MCAL-25614,MCAL-25560,MCAL-25561,MCAL-25569,MCAL-25564,MCAL-25574,MCAL-25567,MCAL-25562,MCAL-25607,MCAL-25608,MCAL-25611,MCAL-25612,MCAL-25606,MCAL-25568,MCAL-25559,MCAL-25573,MCAL-25563,MCAL-25565</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-12327,MCAL-12315,MCAL-12340,MCAL-12359,MCAL-12421,MCAL-12427,MCAL-12341,MCAL-12307,MCAL-12345,MCAL-12391,MCAL-12326,MCAL-12338,MCAL-12414,MCAL-12438,MCAL-12393,MCAL-12362,MCAL-12394,MCAL-12372,MCAL-12376,MCAL-12343,MCAL-12378,MCAL-12342,MCAL-12426,MCAL-12412,MCAL-12329,MCAL-12373,MCAL-12344,MCAL-12308,MCAL-12388,MCAL-12411,MCAL-12346,MCAL-12385,MCAL-12387,MCAL-12353,MCAL-12375,MCAL-12435,MCAL-12354,MCAL-12434,MCAL-12424,MCAL-12347,MCAL-12323,MCAL-12416,MCAL-12306,MCAL-12356,MCAL-12358,MCAL-12374,MCAL-12415,MCAL-12304,MCAL-12377,MCAL-12339</t>
+          <t>MCAL-12327,MCAL-12315,MCAL-12340,MCAL-12359,MCAL-12421,MCAL-12427,MCAL-12341,MCAL-12307,MCAL-12345,MCAL-12391,MCAL-12326,MCAL-12338,MCAL-12414,MCAL-12438,MCAL-12393,MCAL-12362,MCAL-12394,MCAL-12372,MCAL-12376,MCAL-12343,MCAL-12378,MCAL-12342,MCAL-12426,MCAL-12412,MCAL-12329,MCAL-12373,MCAL-12344,MCAL-12308,MCAL-12388,MCAL-12411,MCAL-12346,MCAL-12385,MCAL-12387,MCAL-12353,MCAL-12375,MCAL-12435,MCAL-12354,MCAL-12434,MCAL-12424,MCAL-12347,MCAL-12323,MCAL-12416,MCAL-12306,MCAL-12356,MCAL-12358,MCAL-12374,MCAL-12339,MCAL-12415,MCAL-12304,MCAL-12377</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-24888,MCAL-25066,MCAL-25068,MCAL-25060,MCAL-25061,MCAL-25051,MCAL-25111,MCAL-28292,MCAL-24983,MCAL-24951,MCAL-25059,MCAL-25065,MCAL-24956</t>
+          <t>MCAL-24888,MCAL-25066,MCAL-25068,MCAL-25060,MCAL-25061,MCAL-25051,MCAL-25111,MCAL-28292,MCAL-24983,MCAL-24951,MCAL-24956,MCAL-25065,MCAL-25059</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25158,MCAL-25145,MCAL-25142,MCAL-25171,MCAL-25138,MCAL-25139,MCAL-25140,MCAL-25143,MCAL-25144,MCAL-25146,MCAL-25157,MCAL-25147,MCAL-28104,MCAL-25141</t>
+          <t>MCAL-25158,MCAL-25145,MCAL-25142,MCAL-25171,MCAL-25138,MCAL-25139,MCAL-25140,MCAL-25143,MCAL-25144,MCAL-25146,MCAL-25157,MCAL-25147,MCAL-25141,MCAL-28104</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25107,MCAL-25113,MCAL-24861,MCAL-25108,MCAL-25115,MCAL-25114,MCAL-25105,MCAL-25109,MCAL-25106,MCAL-25110,MCAL-25111,MCAL-25112</t>
+          <t>MCAL-25107,MCAL-25113,MCAL-24861,MCAL-25108,MCAL-25115,MCAL-25114,MCAL-25105,MCAL-25106,MCAL-25110,MCAL-25111,MCAL-25112,MCAL-25109</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>MCAL-24881,MCAL-24878,MCAL-24852,MCAL-24850,MCAL-24890,MCAL-25030,MCAL-25089,MCAL-24877,MCAL-24857,MCAL-24856,MCAL-24851</t>
+          <t>MCAL-24881,MCAL-24878,MCAL-24852,MCAL-24850,MCAL-24890,MCAL-25030,MCAL-25089,MCAL-24877,MCAL-24857,MCAL-24851,MCAL-24856</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30520,MCAL-30527,MCAL-30529,MCAL-30518,MCAL-30531,MCAL-30525,MCAL-30530,MCAL-30532,MCAL-30519,MCAL-30528,MCAL-30521,MCAL-30524,MCAL-30522,MCAL-30523,MCAL-30526</t>
+          <t>MCAL-30520,MCAL-30527,MCAL-30529,MCAL-30518,MCAL-30531,MCAL-30525,MCAL-30530,MCAL-30532,MCAL-30519,MCAL-30528,MCAL-30526,MCAL-30521,MCAL-30524,MCAL-30522,MCAL-30523</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
@@ -15602,7 +15602,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30551,MCAL-30552,MCAL-30554,MCAL-30557,MCAL-30558,MCAL-30569,MCAL-30570,MCAL-30572,MCAL-30575,MCAL-30576,MCAL-30559,MCAL-30563,MCAL-30566,MCAL-30556,MCAL-30553,MCAL-30555,MCAL-30561,MCAL-30573,MCAL-30550,MCAL-30562,MCAL-30564,MCAL-30565,MCAL-30567,MCAL-30568,MCAL-30574,MCAL-30560,MCAL-30571</t>
+          <t>MCAL-30551,MCAL-30552,MCAL-30554,MCAL-30557,MCAL-30558,MCAL-30569,MCAL-30570,MCAL-30572,MCAL-30575,MCAL-30576,MCAL-30559,MCAL-30563,MCAL-30566,MCAL-30556,MCAL-30553,MCAL-30555,MCAL-30561,MCAL-30573,MCAL-30550,MCAL-30562,MCAL-30564,MCAL-30565,MCAL-30567,MCAL-30568,MCAL-30574,MCAL-30571,MCAL-30560</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">

--- a/docs/Test_Report/TestPlanExecutionReport.xlsx
+++ b/docs/Test_Report/TestPlanExecutionReport.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20 11:43:19.837024-06:00 CDT</t>
+          <t>2025-11-20 23:45:26.559499-06:00 CDT</t>
         </is>
       </c>
     </row>
@@ -2624,12 +2624,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Architecture,Design,Design,Design,Design,Design,Design,Architecture,Design,Design,Design,Design,Architecture,Architecture,Architecture,Architecture,Architecture,Design,Architecture</t>
+          <t>Architecture,Design,Design,Design,Design,Design,Design,Architecture,Design,Design,Design,Design,Architecture,Architecture,Architecture,Design,Architecture,Architecture,Architecture</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25189,MCAL-25530,MCAL-25533,MCAL-25534,MCAL-25535,MCAL-25538,MCAL-25540,MCAL-25190,MCAL-25531,MCAL-25532,MCAL-25537,MCAL-25539,MCAL-28233,MCAL-25192,MCAL-25194,MCAL-25195,MCAL-25191,MCAL-25536,MCAL-25193</t>
+          <t>MCAL-25189,MCAL-25530,MCAL-25533,MCAL-25534,MCAL-25535,MCAL-25538,MCAL-25540,MCAL-25190,MCAL-25531,MCAL-25532,MCAL-25537,MCAL-25539,MCAL-28233,MCAL-25192,MCAL-25194,MCAL-25536,MCAL-25195,MCAL-25191,MCAL-25193</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">

--- a/docs/Test_Report/TestPlanExecutionReport.xlsx
+++ b/docs/Test_Report/TestPlanExecutionReport.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20 23:45:26.559499-06:00 CDT</t>
+          <t>2025-12-09 03:49:21.018922-06:00 CDT</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28162,MCAL-28163,MCAL-25808,MCAL-25806,MCAL-25807,MCAL-25801,MCAL-25799,MCAL-25800,MCAL-25820,MCAL-28165,MCAL-28164,MCAL-25797,MCAL-25812,MCAL-25811,MCAL-25810,MCAL-28161,MCAL-25809,MCAL-25804,MCAL-25803,MCAL-25802,MCAL-25798,MCAL-25796,MCAL-25805</t>
+          <t>MCAL-28162,MCAL-28163,MCAL-25808,MCAL-25806,MCAL-25807,MCAL-25801,MCAL-25799,MCAL-28164,MCAL-25811,MCAL-25810,MCAL-25805,MCAL-25800,MCAL-25796,MCAL-25820,MCAL-28165,MCAL-25797,MCAL-25812,MCAL-28161,MCAL-25809,MCAL-25804,MCAL-25803,MCAL-25802,MCAL-25798</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25814,MCAL-25721,MCAL-25720,MCAL-25717,MCAL-25712,MCAL-25711,MCAL-25701,MCAL-25715,MCAL-25704,MCAL-25702,MCAL-25716,MCAL-25718,MCAL-25706,MCAL-25709,MCAL-25708,MCAL-25707,MCAL-25813,MCAL-25723,MCAL-25731,MCAL-25727,MCAL-25726,MCAL-25724,MCAL-25725,MCAL-28133,MCAL-25703,MCAL-25824,MCAL-25823,MCAL-25732,MCAL-25722,MCAL-25719,MCAL-28135,MCAL-25825,MCAL-25710,MCAL-25705,MCAL-25714,MCAL-25713,MCAL-28134,MCAL-25822,MCAL-25730,MCAL-25729,MCAL-25728</t>
+          <t>MCAL-25814,MCAL-25721,MCAL-25720,MCAL-25717,MCAL-25712,MCAL-25711,MCAL-25701,MCAL-25715,MCAL-25704,MCAL-25702,MCAL-25716,MCAL-25718,MCAL-25709,MCAL-25708,MCAL-25707,MCAL-25706,MCAL-25725,MCAL-25703,MCAL-25813,MCAL-25732,MCAL-25722,MCAL-25719,MCAL-25710,MCAL-25705,MCAL-25714,MCAL-25713,MCAL-25728,MCAL-25731,MCAL-25727,MCAL-25726,MCAL-25724,MCAL-28133,MCAL-25824,MCAL-25823,MCAL-28135,MCAL-25825,MCAL-28134,MCAL-25822,MCAL-25730,MCAL-25729,MCAL-25723</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Architecture,Design,Design,Design,Design,Design,Design,Architecture,Design,Design,Design,Design,Architecture,Architecture,Architecture,Design,Architecture,Architecture,Architecture</t>
+          <t>Architecture,Design,Design,Design,Design,Design,Design,Architecture,Design,Design,Design,Design,Architecture,Architecture,Architecture,Architecture,Design,Architecture,Architecture</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25189,MCAL-25530,MCAL-25533,MCAL-25534,MCAL-25535,MCAL-25538,MCAL-25540,MCAL-25190,MCAL-25531,MCAL-25532,MCAL-25537,MCAL-25539,MCAL-28233,MCAL-25192,MCAL-25194,MCAL-25536,MCAL-25195,MCAL-25191,MCAL-25193</t>
+          <t>MCAL-25189,MCAL-25530,MCAL-25533,MCAL-25534,MCAL-25535,MCAL-25538,MCAL-25540,MCAL-25190,MCAL-25531,MCAL-25532,MCAL-25537,MCAL-25539,MCAL-28233,MCAL-25191,MCAL-25192,MCAL-25194,MCAL-25536,MCAL-25195,MCAL-25193</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Architecture,Design,Architecture,Design,Architecture,Design,Design,Architecture,Architecture,Design,Architecture,Architecture,Design,Design</t>
+          <t>Architecture,Design,Architecture,Design,Design,Architecture,Design,Design,Architecture,Architecture,Architecture,Architecture,Design,Design</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25190,MCAL-25592,MCAL-25191,MCAL-25590,MCAL-25195,MCAL-25591,MCAL-25688,MCAL-25193,MCAL-25189,MCAL-25690,MCAL-25192,MCAL-25194,MCAL-25691,MCAL-25689</t>
+          <t>MCAL-25190,MCAL-25592,MCAL-25191,MCAL-25590,MCAL-25690,MCAL-25195,MCAL-25591,MCAL-25688,MCAL-25193,MCAL-25189,MCAL-25192,MCAL-25194,MCAL-25691,MCAL-25689</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25560,MCAL-25565,MCAL-25569,MCAL-25572,MCAL-25607,MCAL-25609,MCAL-25675,MCAL-25636,MCAL-25567,MCAL-25568,MCAL-25574,MCAL-25606,MCAL-25683,MCAL-25635,MCAL-25610,MCAL-25638,MCAL-25562,MCAL-25559,MCAL-25563,MCAL-25608,MCAL-25698,MCAL-25673,MCAL-25688,MCAL-25696,MCAL-25637,MCAL-25678,MCAL-25573</t>
+          <t>MCAL-25560,MCAL-25565,MCAL-25569,MCAL-25572,MCAL-25607,MCAL-25609,MCAL-25675,MCAL-25636,MCAL-25567,MCAL-25568,MCAL-25574,MCAL-25606,MCAL-25683,MCAL-25635,MCAL-25610,MCAL-25638,MCAL-25562,MCAL-25559,MCAL-25678,MCAL-25573,MCAL-25563,MCAL-25608,MCAL-25698,MCAL-25673,MCAL-25688,MCAL-25696,MCAL-25637</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture</t>
+          <t>Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-12327,MCAL-12315,MCAL-12340,MCAL-12359,MCAL-12421,MCAL-12427,MCAL-12341,MCAL-12307,MCAL-12345,MCAL-12391,MCAL-12326,MCAL-12338,MCAL-12414,MCAL-12438,MCAL-12393,MCAL-12362,MCAL-12394,MCAL-12372,MCAL-12376,MCAL-12343,MCAL-12378,MCAL-12342,MCAL-12426,MCAL-12412,MCAL-12329,MCAL-12373,MCAL-12344,MCAL-12308,MCAL-12388,MCAL-12411,MCAL-12346,MCAL-12385,MCAL-12387,MCAL-12353,MCAL-12375,MCAL-12435,MCAL-12354,MCAL-12434,MCAL-12424,MCAL-12347,MCAL-12323,MCAL-12416,MCAL-12306,MCAL-12356,MCAL-12358,MCAL-12374,MCAL-12339,MCAL-12415,MCAL-12304,MCAL-12377</t>
+          <t>MCAL-12327,MCAL-12315,MCAL-12340,MCAL-12359,MCAL-12421,MCAL-12427,MCAL-12341,MCAL-12307,MCAL-12345,MCAL-12391,MCAL-12326,MCAL-12338,MCAL-12414,MCAL-12438,MCAL-12393,MCAL-12362,MCAL-12394,MCAL-12372,MCAL-12376,MCAL-12343,MCAL-12378,MCAL-12342,MCAL-12426,MCAL-12412,MCAL-12329,MCAL-12373,MCAL-12344,MCAL-12308,MCAL-12388,MCAL-12411,MCAL-12346,MCAL-12385,MCAL-12387,MCAL-12353,MCAL-12375,MCAL-12435,MCAL-12354,MCAL-12434,MCAL-12424,MCAL-12347,MCAL-12323,MCAL-12416,MCAL-12306,MCAL-12356,MCAL-12358,MCAL-12374,MCAL-12415,MCAL-12304,MCAL-12377</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-24888,MCAL-25066,MCAL-25068,MCAL-25060,MCAL-25061,MCAL-25051,MCAL-25111,MCAL-28292,MCAL-24983,MCAL-24951,MCAL-24956,MCAL-25065,MCAL-25059</t>
+          <t>MCAL-24888,MCAL-25066,MCAL-25068,MCAL-25060,MCAL-25061,MCAL-25051,MCAL-25111,MCAL-28292,MCAL-24983,MCAL-24951,MCAL-25059,MCAL-25065,MCAL-24956</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25158,MCAL-25145,MCAL-25142,MCAL-25171,MCAL-25138,MCAL-25139,MCAL-25140,MCAL-25143,MCAL-25144,MCAL-25146,MCAL-25157,MCAL-25147,MCAL-25141,MCAL-28104</t>
+          <t>MCAL-25158,MCAL-25145,MCAL-25142,MCAL-25171,MCAL-25138,MCAL-25139,MCAL-25140,MCAL-25143,MCAL-25144,MCAL-25146,MCAL-25157,MCAL-25147,MCAL-28104,MCAL-25141</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30520,MCAL-30527,MCAL-30529,MCAL-30518,MCAL-30531,MCAL-30525,MCAL-30530,MCAL-30532,MCAL-30519,MCAL-30528,MCAL-30526,MCAL-30521,MCAL-30524,MCAL-30522,MCAL-30523</t>
+          <t>MCAL-30520,MCAL-30527,MCAL-30529,MCAL-30518,MCAL-30531,MCAL-30525,MCAL-30530,MCAL-30532,MCAL-30519,MCAL-30528,MCAL-30521,MCAL-30524,MCAL-30522,MCAL-30523,MCAL-30526</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
@@ -15602,7 +15602,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30551,MCAL-30552,MCAL-30554,MCAL-30557,MCAL-30558,MCAL-30569,MCAL-30570,MCAL-30572,MCAL-30575,MCAL-30576,MCAL-30559,MCAL-30563,MCAL-30566,MCAL-30556,MCAL-30553,MCAL-30555,MCAL-30561,MCAL-30573,MCAL-30550,MCAL-30562,MCAL-30564,MCAL-30565,MCAL-30567,MCAL-30568,MCAL-30574,MCAL-30571,MCAL-30560</t>
+          <t>MCAL-30551,MCAL-30552,MCAL-30554,MCAL-30557,MCAL-30558,MCAL-30569,MCAL-30570,MCAL-30572,MCAL-30575,MCAL-30576,MCAL-30559,MCAL-30563,MCAL-30566,MCAL-30556,MCAL-30553,MCAL-30555,MCAL-30561,MCAL-30573,MCAL-30550,MCAL-30562,MCAL-30564,MCAL-30565,MCAL-30567,MCAL-30568,MCAL-30574,MCAL-30560,MCAL-30571</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
